--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/metropolitana.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/metropolitana.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>19323.55</v>
+        <v>19224.27</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25378.09</v>
+        <v>25124.81</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>74017.50999999999</v>
+        <v>73278.81</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>23914.52</v>
+        <v>23648.08</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>49881.7</v>
+        <v>49325.94</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>53398.29</v>
+        <v>52803.36</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>242295.64</v>
+        <v>240968.72</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>26135.05</v>
+        <v>25991.92</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>53770.8</v>
+        <v>53702.36</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>57517.96</v>
+        <v>57444.75</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>57517.96</v>
+        <v>57444.75</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>53780.59</v>
+        <v>53972.52</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>28770.05</v>
+        <v>28864.67</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>28770.05</v>
+        <v>28864.67</v>
       </c>
     </row>
     <row r="16">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>238458.48</v>
+        <v>242574.63</v>
       </c>
     </row>
     <row r="17">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>210224.67</v>
+        <v>213853.47</v>
       </c>
     </row>
     <row r="18">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>21718.56</v>
+        <v>21869.01</v>
       </c>
     </row>
     <row r="19">
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>35877.83</v>
+        <v>36126.38</v>
       </c>
     </row>
     <row r="20">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>23952.6</v>
+        <v>24064.15</v>
       </c>
     </row>
     <row r="21">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>10284.62</v>
+        <v>10332.52</v>
       </c>
     </row>
     <row r="22">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>33348.28</v>
+        <v>33503.59</v>
       </c>
     </row>
     <row r="23">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>17156.29</v>
+        <v>17279.98</v>
       </c>
     </row>
     <row r="24">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>25383.2</v>
+        <v>25338.18</v>
       </c>
     </row>
     <row r="25">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>67279.63</v>
+        <v>67160.3</v>
       </c>
     </row>
     <row r="26">
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>25383.2</v>
+        <v>25278.59</v>
       </c>
     </row>
     <row r="27">
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>77787.06</v>
+        <v>77666.49000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>71532.96000000001</v>
+        <v>71422.09</v>
       </c>
     </row>
     <row r="29">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>25276.22</v>
+        <v>25237.05</v>
       </c>
     </row>
     <row r="30">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>35766.48</v>
+        <v>35711.05</v>
       </c>
     </row>
     <row r="31">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>41640.32</v>
+        <v>41855.37</v>
       </c>
     </row>
     <row r="32">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>41182.73</v>
+        <v>41395.42</v>
       </c>
     </row>
     <row r="33">
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>41718.08</v>
+        <v>41933.53</v>
       </c>
     </row>
     <row r="34">
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>19446.76</v>
+        <v>19547.2</v>
       </c>
     </row>
     <row r="35">
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>41718.08</v>
+        <v>41933.53</v>
       </c>
     </row>
     <row r="36">
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>43687.79</v>
+        <v>43996.12</v>
       </c>
     </row>
     <row r="37">
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>45955.02</v>
+        <v>46279.36</v>
       </c>
     </row>
     <row r="38">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>48739.81</v>
+        <v>49083.79</v>
       </c>
     </row>
     <row r="39">
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>49881.7</v>
+        <v>50233.74</v>
       </c>
     </row>
     <row r="40">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>37209.85</v>
+        <v>36737.2</v>
       </c>
     </row>
     <row r="41">
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>66277.28999999999</v>
+        <v>66039.63</v>
       </c>
     </row>
     <row r="42">
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>169795.78</v>
+        <v>167830.71</v>
       </c>
     </row>
     <row r="43">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>21030.42</v>
+        <v>20787.03</v>
       </c>
     </row>
     <row r="44">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>17522.1</v>
+        <v>17319.32</v>
       </c>
     </row>
     <row r="45">
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>63091.25</v>
+        <v>62361.09</v>
       </c>
     </row>
     <row r="46">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>26196.21</v>
+        <v>25974.31</v>
       </c>
     </row>
     <row r="47">
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>26174.04</v>
+        <v>25952.33</v>
       </c>
     </row>
     <row r="48">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>59359.52</v>
+        <v>58856.7</v>
       </c>
     </row>
     <row r="49">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>42289.44</v>
+        <v>41931.21</v>
       </c>
     </row>
     <row r="50">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>21007.82</v>
+        <v>20829.86</v>
       </c>
     </row>
     <row r="51">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>25082.71</v>
+        <v>24870.24</v>
       </c>
     </row>
     <row r="52">
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>29778.33</v>
+        <v>29754.39</v>
       </c>
     </row>
     <row r="53">
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>20596.44</v>
+        <v>20579.89</v>
       </c>
     </row>
     <row r="54">
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>11090.82</v>
+        <v>11133.39</v>
       </c>
     </row>
     <row r="55">
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>580067.77</v>
+        <v>582696.4300000001</v>
       </c>
     </row>
     <row r="56">
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>290657.08</v>
+        <v>291974.24</v>
       </c>
     </row>
     <row r="57">
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>25527.77</v>
+        <v>25643.45</v>
       </c>
     </row>
     <row r="58">
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>59595.92</v>
+        <v>59865.99</v>
       </c>
     </row>
     <row r="59">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>93814.64</v>
+        <v>94063.41</v>
       </c>
     </row>
     <row r="60">
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>16478.4</v>
+        <v>16455.28</v>
       </c>
     </row>
     <row r="61">
@@ -4204,7 +4204,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>279545.37</v>
+        <v>279903.74</v>
       </c>
     </row>
     <row r="62">
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>24463.31</v>
+        <v>24494.68</v>
       </c>
     </row>
     <row r="63">
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>37396.5</v>
+        <v>37653.91</v>
       </c>
     </row>
     <row r="64">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>30316.22</v>
+        <v>30524.89</v>
       </c>
     </row>
     <row r="65">
@@ -4448,7 +4448,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>31786.1</v>
+        <v>32004.89</v>
       </c>
     </row>
     <row r="66">
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>26566.96</v>
+        <v>26749.82</v>
       </c>
     </row>
     <row r="67">
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>10503.91</v>
+        <v>10616.58</v>
       </c>
     </row>
     <row r="68">
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>94856.52</v>
+        <v>95375.27</v>
       </c>
     </row>
     <row r="69">
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>29308.25</v>
+        <v>28936.25</v>
       </c>
     </row>
     <row r="70">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>124884.17</v>
+        <v>124455.56</v>
       </c>
     </row>
     <row r="71">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>21432.95</v>
+        <v>21954.15</v>
       </c>
     </row>
     <row r="72">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>46936.21</v>
+        <v>48077.59</v>
       </c>
     </row>
     <row r="73">
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>27049.47</v>
+        <v>27869.69</v>
       </c>
     </row>
     <row r="74">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>36638.34</v>
+        <v>37727.35</v>
       </c>
     </row>
     <row r="75">
@@ -5066,7 +5066,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>55324.7</v>
+        <v>54910.65</v>
       </c>
     </row>
     <row r="76">
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>37571.1</v>
+        <v>37912.84</v>
       </c>
     </row>
     <row r="77">
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>38225.45</v>
+        <v>38491.58</v>
       </c>
     </row>
     <row r="78">
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>11474.21</v>
+        <v>11454.55</v>
       </c>
     </row>
     <row r="79">
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>26084.14</v>
+        <v>26045.77</v>
       </c>
     </row>
     <row r="80">
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>26305.98</v>
+        <v>26204.45</v>
       </c>
     </row>
     <row r="81">
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>22948.42</v>
+        <v>22859.85</v>
       </c>
     </row>
     <row r="82">
@@ -5493,7 +5493,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>50511.59</v>
+        <v>50773.11</v>
       </c>
     </row>
     <row r="83">
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>43905.43</v>
+        <v>43340.19</v>
       </c>
     </row>
     <row r="84">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>36619.68</v>
+        <v>36148.24</v>
       </c>
     </row>
     <row r="85">
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>25707.41</v>
+        <v>25376.45</v>
       </c>
     </row>
     <row r="86">
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>36619.68</v>
+        <v>36148.24</v>
       </c>
     </row>
     <row r="87">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>18882.44</v>
+        <v>18749.18</v>
       </c>
     </row>
     <row r="88">
@@ -5859,7 +5859,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>13503.68</v>
+        <v>13748.51</v>
       </c>
     </row>
     <row r="89">
@@ -5920,7 +5920,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>12766</v>
+        <v>12965.98</v>
       </c>
     </row>
     <row r="90">
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>27675.77</v>
+        <v>27790.1</v>
       </c>
     </row>
     <row r="91">
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>26813.45</v>
+        <v>26503.91</v>
       </c>
     </row>
     <row r="92">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>26789.77</v>
+        <v>26390.2</v>
       </c>
     </row>
     <row r="93">
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>53414.91</v>
+        <v>52618.21</v>
       </c>
     </row>
     <row r="94">
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>17644.15</v>
+        <v>17568.13</v>
       </c>
     </row>
     <row r="95">
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>24052.33</v>
+        <v>23948.71</v>
       </c>
     </row>
     <row r="96">
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>27685.67</v>
+        <v>27041.45</v>
       </c>
     </row>
     <row r="97">
@@ -6408,7 +6408,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>31642.18</v>
+        <v>30905.89</v>
       </c>
     </row>
     <row r="98">
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>21335.18</v>
+        <v>20838.73</v>
       </c>
     </row>
     <row r="99">
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>30285.23</v>
+        <v>29736.01</v>
       </c>
     </row>
     <row r="100">
@@ -6591,7 +6591,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>13684.26</v>
+        <v>13436.1</v>
       </c>
     </row>
     <row r="101">
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>42225.17</v>
+        <v>42400.66</v>
       </c>
     </row>
     <row r="102">
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>41783.23</v>
+        <v>42297.47</v>
       </c>
     </row>
     <row r="103">
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>13834.64</v>
+        <v>13959.27</v>
       </c>
     </row>
     <row r="104">
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>13486.6</v>
+        <v>13428.66</v>
       </c>
     </row>
     <row r="105">
@@ -6896,7 +6896,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>17165.73</v>
+        <v>17357.71</v>
       </c>
     </row>
     <row r="106">
@@ -6957,7 +6957,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>35281.6</v>
+        <v>35415.26</v>
       </c>
     </row>
     <row r="107">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>39953.46</v>
+        <v>40333.05</v>
       </c>
     </row>
     <row r="108">
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>29685.11</v>
+        <v>29906.26</v>
       </c>
     </row>
     <row r="109">
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>74376.7</v>
+        <v>74050.67999999999</v>
       </c>
     </row>
     <row r="110">
@@ -7201,7 +7201,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>25640.39</v>
+        <v>25361.47</v>
       </c>
     </row>
     <row r="111">
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>41735.74</v>
+        <v>41281.73</v>
       </c>
     </row>
     <row r="112">
@@ -7323,7 +7323,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>57276.38</v>
+        <v>57146.37</v>
       </c>
     </row>
     <row r="113">
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>39361.41</v>
+        <v>39491.98</v>
       </c>
     </row>
     <row r="114">
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>52246.83</v>
+        <v>51364.08</v>
       </c>
     </row>
     <row r="115">
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>25439.45</v>
+        <v>25089.9</v>
       </c>
     </row>
     <row r="116">
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>78885.42999999999</v>
+        <v>77801.52</v>
       </c>
     </row>
     <row r="117">
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>36766.29</v>
+        <v>37465.27</v>
       </c>
     </row>
     <row r="118">
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>73294.95</v>
+        <v>73521.55</v>
       </c>
     </row>
     <row r="119">
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>27885.14</v>
+        <v>27811.39</v>
       </c>
     </row>
     <row r="120">
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>603.08</v>
+        <v>601.49</v>
       </c>
     </row>
     <row r="121">
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>30235.3</v>
+        <v>30155.34</v>
       </c>
     </row>
     <row r="122">
@@ -7933,7 +7933,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>40571.88</v>
+        <v>40031.46</v>
       </c>
     </row>
     <row r="123">
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>120712.8</v>
+        <v>121520.79</v>
       </c>
     </row>
     <row r="124">
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>15940.47</v>
+        <v>15908.52</v>
       </c>
     </row>
     <row r="125">
@@ -8120,7 +8120,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>75591.86</v>
+        <v>75440.33</v>
       </c>
     </row>
     <row r="126">
@@ -8181,7 +8181,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>169017.9</v>
+        <v>166290.37</v>
       </c>
     </row>
     <row r="127">
@@ -8242,7 +8242,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>32923.19</v>
+        <v>32391.89</v>
       </c>
     </row>
     <row r="128">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>693.99</v>
+        <v>682.79</v>
       </c>
     </row>
     <row r="129">
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>22719.1</v>
+        <v>22354.83</v>
       </c>
     </row>
     <row r="130">
@@ -8425,7 +8425,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>32224.45</v>
+        <v>31707.78</v>
       </c>
     </row>
     <row r="131">
@@ -8486,7 +8486,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>46897.23</v>
+        <v>47211.13</v>
       </c>
     </row>
     <row r="132">
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>17186.38</v>
+        <v>17301.41</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/metropolitana.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M132"/>
+  <dimension ref="A1:M144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1426037-152-CM25</t>
+          <t>630-16-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.941.900-5</t>
+          <t>61.501.000-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>SUBSECRETARIA DEL TRABAJO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>19224.27</v>
+        <v>19550.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>48-336-CM25</t>
+          <t>2732-8-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.812.000-7</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25124.81</v>
+        <v>22379.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1216062-1056-CM25</t>
+          <t>1590-155-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>71.265.200-4</t>
+          <t>61.301.000-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Lo Prado</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>73278.81</v>
+        <v>45240.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1389488-69-CM25</t>
+          <t>1018-47-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.981.320-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LOS ÁLAMOS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>23648.08</v>
+        <v>24951.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>967490-57-CM25</t>
+          <t>4629-311-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>49325.94</v>
+        <v>31926.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3316-318-CM25</t>
+          <t>1593-252-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.221.000-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>52803.36</v>
+        <v>25859.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2723-241-CM25</t>
+          <t>1211839-7256-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.072.500-2</t>
+          <t>70.856.400-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BUIN</t>
+          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,32 +920,28 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>81.318.700-0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>240968.72</v>
+        <v>27864.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1098710-463-CM25</t>
+          <t>758004-123-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -955,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.000.740-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -985,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1000,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>25991.92</v>
+        <v>41842.64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3326-555-CM25</t>
+          <t>5178-3574-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1031,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1046,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1061,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>53702.36</v>
+        <v>66312.53</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3323-118-CM25</t>
+          <t>2933-295-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.073.200-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>I MUNICIPALIDAD DE ALHUE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1107,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>57444.75</v>
+        <v>19747.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3453-590-CM25</t>
+          <t>539119-7588-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1153,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>57444.75</v>
+        <v>67461.47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2673-219-CM25</t>
+          <t>2933-371-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1214,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>69.073.200-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>I MUNICIPALIDAD DE ALHUE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1229,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>53972.52</v>
+        <v>51000.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3474-818-CM25</t>
+          <t>1426037-152-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1275,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>70.941.900-5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>28864.67</v>
+        <v>19224.27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3474-819-CM25</t>
+          <t>48-336-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1326,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.812.000-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1351,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>28864.67</v>
+        <v>25124.81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3326-552-CM25</t>
+          <t>1216062-1056-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1387,22 +1383,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>71.265.200-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Corporación Municipal de Lo Prado</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1412,32 +1408,28 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>242574.63</v>
+        <v>73278.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3326-551-CM25</t>
+          <t>1389488-69-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1452,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1462,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.981.320-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LOS ÁLAMOS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1477,32 +1469,28 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
-        </is>
-      </c>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>213853.47</v>
+        <v>23648.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3813-30-CM25</t>
+          <t>967490-57-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1517,22 +1505,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.071.900-2</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ISLA DE MAIPO</t>
+          <t>Dirección General de Carabineros de Chile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1542,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1557,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>21869.01</v>
+        <v>49325.94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3666-55-CM25</t>
+          <t>3316-318-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1578,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1588,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.071.600-3</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIL TIL</t>
+          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1603,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1618,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>36126.38</v>
+        <v>52803.36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>425-843-CM25</t>
+          <t>2723-241-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1639,22 +1627,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.072.500-2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE BUIN</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1664,28 +1652,32 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>24064.15</v>
+        <v>240968.72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2412-1059-CM25</t>
+          <t>1098710-463-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1700,22 +1692,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>62.000.740-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1725,12 +1717,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1740,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>10332.52</v>
+        <v>25991.92</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>707428-157-CM25</t>
+          <t>3326-555-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1761,7 +1753,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1771,12 +1763,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1786,12 +1778,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1801,13 +1793,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>33503.59</v>
+        <v>53702.36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>539119-10421-CM25</t>
+          <t>3323-118-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1822,7 +1814,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1832,12 +1824,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1847,12 +1839,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1862,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>17279.98</v>
+        <v>57444.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>587-795-CM25</t>
+          <t>3453-590-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1883,7 +1875,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1893,12 +1885,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1908,12 +1900,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1923,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>25338.18</v>
+        <v>57444.75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5482-144-CM25</t>
+          <t>2673-219-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1944,7 +1936,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1954,12 +1946,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.070.500-1</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUNOA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1969,12 +1961,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1984,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>67160.3</v>
+        <v>53972.52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>784642-53-CM25</t>
+          <t>3474-819-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2005,7 +1997,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2020,7 +2012,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Car</t>
+          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2030,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2045,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>25278.59</v>
+        <v>28864.67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3326-545-CM25</t>
+          <t>3474-818-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2066,7 +2058,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2076,12 +2068,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2091,32 +2083,28 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>77666.49000000001</v>
+        <v>28864.67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>634-1055-CM25</t>
+          <t>3326-552-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2131,7 +2119,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2141,12 +2129,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.004.000-4</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2156,28 +2144,32 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>71422.09</v>
+        <v>242574.63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1147293-331-CM25</t>
+          <t>3326-551-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2192,22 +2184,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.930.000-8</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fundación para la Innovación Agraria</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2217,28 +2209,32 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>25237.05</v>
+        <v>213853.47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>634-1060-CM25</t>
+          <t>3813-30-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2253,22 +2249,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.004.000-4</t>
+          <t>69.071.900-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE ISLA DE MAIPO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2278,12 +2274,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2293,13 +2289,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>35711.05</v>
+        <v>21869.01</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1447930-322-CM25</t>
+          <t>3666-55-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2314,7 +2310,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2324,12 +2320,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.999.390-K</t>
+          <t>69.071.600-3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE TIL TIL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2339,12 +2335,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2354,13 +2350,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>41855.37</v>
+        <v>36126.38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2271-230-CM25</t>
+          <t>707428-157-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2375,22 +2371,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2400,12 +2396,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2415,13 +2411,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>41395.42</v>
+        <v>33503.59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2981-1601-CM25</t>
+          <t>2412-1059-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2436,7 +2432,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2446,12 +2442,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2461,12 +2457,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2476,13 +2472,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>41933.53</v>
+        <v>10332.52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2767-124-CM25</t>
+          <t>425-843-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2497,7 +2493,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2507,12 +2503,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2522,12 +2518,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2537,13 +2533,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>19547.2</v>
+        <v>24064.15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5890-187-CM25</t>
+          <t>539119-10421-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2558,7 +2554,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2568,12 +2564,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>Carabineros de Chile - Dirección de Bienestar</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2583,12 +2579,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2598,13 +2594,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>41933.53</v>
+        <v>17279.98</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2673-227-CM25</t>
+          <t>587-795-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2619,22 +2615,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2644,12 +2640,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2659,13 +2655,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>43996.12</v>
+        <v>25338.18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2974-641-CM25</t>
+          <t>5482-144-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2680,22 +2676,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>69.070.500-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2705,12 +2701,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2720,13 +2716,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>46279.36</v>
+        <v>67160.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>29-589-CM25</t>
+          <t>784642-53-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2741,7 +2737,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2751,12 +2747,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>Dirección de Educación, Doctrina e Historia de Car</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2766,12 +2762,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2781,13 +2777,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>49083.79</v>
+        <v>25278.59</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3326-597-CM25</t>
+          <t>3326-545-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2802,7 +2798,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2827,28 +2823,32 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>50233.74</v>
+        <v>77666.49000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2483-878-CM25</t>
+          <t>634-1055-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2858,27 +2858,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>61.004.000-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTOMOTORA MELHUISH SPA </t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.281.300-9</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2903,13 +2903,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>36737.2</v>
+        <v>71422.09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3326-610-CM25</t>
+          <t>1147293-331-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2919,27 +2919,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>70.930.000-8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Fundación para la Innovación Agraria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2964,13 +2964,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>66039.63</v>
+        <v>25237.05</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1867-331-CM25</t>
+          <t>634-1060-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2995,12 +2995,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.110.000-0</t>
+          <t>61.004.000-4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE MOVILIZACIONN NACIONAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3010,32 +3010,28 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.889.440-4</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>167830.71</v>
+        <v>35711.05</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2271-234-CM25</t>
+          <t>2271-230-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3045,12 +3041,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3090,13 +3086,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>20787.03</v>
+        <v>41395.42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1375746-100-CM25</t>
+          <t>2981-1601-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3106,12 +3102,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3121,12 +3117,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.981.280-8</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3136,12 +3132,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3151,13 +3147,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>17319.32</v>
+        <v>41933.53</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2018-260-CM25</t>
+          <t>1447930-322-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3167,27 +3163,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.999.390-K</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3197,12 +3193,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3212,13 +3208,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>62361.09</v>
+        <v>41855.37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1375753-101-CM25</t>
+          <t>2767-124-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3228,27 +3224,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.981.290-5</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3258,12 +3254,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3273,13 +3269,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>25974.31</v>
+        <v>19547.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1375757-103-CM25</t>
+          <t>5890-187-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3289,12 +3285,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3304,12 +3300,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3319,12 +3315,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3334,13 +3330,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>25952.33</v>
+        <v>41933.53</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3326-621-CM25</t>
+          <t>29-589-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3350,12 +3346,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3365,12 +3361,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3380,12 +3376,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3395,13 +3391,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>58856.7</v>
+        <v>49083.79</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>545774-88-CM25</t>
+          <t>3326-597-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3411,27 +3407,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.070.800-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3441,12 +3437,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3456,13 +3452,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>41931.21</v>
+        <v>50233.74</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>545774-87-CM25</t>
+          <t>2974-641-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3472,12 +3468,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3487,12 +3483,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.070.800-0</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
+          <t>Division de Bienestar Social</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3502,12 +3498,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3517,13 +3513,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>20829.86</v>
+        <v>46279.36</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1375760-71-CM25</t>
+          <t>2673-227-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3533,27 +3529,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.981.310-3</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3563,12 +3559,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3578,13 +3574,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>24870.24</v>
+        <v>43996.12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5482-152-CM25</t>
+          <t>2483-878-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3599,7 +3595,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3609,12 +3605,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.070.500-1</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUNOA</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3624,12 +3620,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t xml:space="preserve">AUTOMOTORA MELHUISH SPA </t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>76.281.300-9</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3639,13 +3635,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>29754.39</v>
+        <v>36737.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3326-624-CM25</t>
+          <t>3326-610-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3660,7 +3656,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3685,12 +3681,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3700,13 +3696,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>20579.89</v>
+        <v>66039.63</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3658-846-CM25</t>
+          <t>2271-234-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3721,7 +3717,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3731,12 +3727,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.072.800-1</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALERA DE TANGO</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3746,12 +3742,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3761,13 +3757,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>11133.39</v>
+        <v>20787.03</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>979-2135-CM25</t>
+          <t>1867-331-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3782,22 +3778,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.110.000-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION GENERAL DE MOVILIZACIONN NACIONAL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3807,12 +3803,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3826,13 +3822,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>582696.4300000001</v>
+        <v>167830.71</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5240-296-CM25</t>
+          <t>2018-260-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3847,22 +3843,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3872,32 +3868,28 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>291974.24</v>
+        <v>62361.09</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1375761-114-CM25</t>
+          <t>1375746-100-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3912,7 +3904,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3922,12 +3914,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>61.981.280-8</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3937,12 +3929,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3952,13 +3944,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>25643.45</v>
+        <v>17319.32</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5482-155-CM25</t>
+          <t>1375757-103-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3973,22 +3965,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.070.500-1</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUNOA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3998,12 +3990,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4013,13 +4005,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>59865.99</v>
+        <v>25952.33</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2686-787-CM25</t>
+          <t>545774-87-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4034,22 +4026,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.071.500-7</t>
+          <t>69.070.800-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLINA</t>
+          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4059,32 +4051,28 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de los Lagos </t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>94063.41</v>
+        <v>20829.86</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1214069-336-CM25</t>
+          <t>3326-621-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4099,7 +4087,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4109,12 +4097,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>70.878.100-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE CONCHALI DE EDUCACION SALUD Y ATENCION DE MENORES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4124,12 +4112,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4139,13 +4127,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>16455.28</v>
+        <v>58856.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3326-606-CM25</t>
+          <t>1375753-101-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4160,7 +4148,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4170,12 +4158,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.981.290-5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS ANDES</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4185,32 +4173,28 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>279903.74</v>
+        <v>25974.31</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>425-974-CM25</t>
+          <t>1375760-71-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4225,22 +4209,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.981.310-3</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4250,12 +4234,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4265,13 +4249,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>24494.68</v>
+        <v>24870.24</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2483-975-CM25</t>
+          <t>545774-88-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4286,7 +4270,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4296,12 +4280,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>69.070.800-0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4311,12 +4295,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4326,13 +4310,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>37653.91</v>
+        <v>41931.21</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1385462-299-CM25</t>
+          <t>5482-152-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4347,22 +4331,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.070.500-1</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4372,12 +4356,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4387,13 +4371,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>30524.89</v>
+        <v>29754.39</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1216088-354-CM25</t>
+          <t>3326-624-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4408,22 +4392,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>65.065.121-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4433,12 +4417,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4448,13 +4432,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>32004.89</v>
+        <v>20579.89</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>48-425-CM25</t>
+          <t>3658-846-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4469,22 +4453,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.812.000-7</t>
+          <t>69.072.800-1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE CALERA DE TANGO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4494,12 +4478,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4509,13 +4493,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>26749.82</v>
+        <v>11133.39</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2455-213-CM25</t>
+          <t>979-2135-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4530,22 +4514,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.071.000-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4555,28 +4539,32 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>10616.58</v>
+        <v>582696.4300000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2560-127-CM25</t>
+          <t>5240-296-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4591,22 +4579,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4635,13 +4623,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>95375.27</v>
+        <v>291974.24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1404452-2-CM26</t>
+          <t>1375761-114-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4651,12 +4639,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4666,12 +4654,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>65.060.484-9</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES PARQUE CORDILLERA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4696,13 +4684,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>28936.25</v>
+        <v>25643.45</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2560-141-CM25</t>
+          <t>5482-155-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4712,12 +4700,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4727,12 +4715,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>69.070.500-1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4742,32 +4730,28 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>124455.56</v>
+        <v>59865.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1350104-5-CM26</t>
+          <t>2686-787-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4777,12 +4761,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4792,12 +4776,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>65.084.447-5</t>
+          <t>69.071.500-7</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN DE MUNICIPALIDADES DE LA PROVINCIA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE COLINA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4807,28 +4791,32 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>21954.15</v>
+        <v>94063.41</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3326-39-CM26</t>
+          <t>1214069-336-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4838,12 +4826,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4853,12 +4841,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>70.878.100-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP MUNICIPAL DE CONCHALI DE EDUCACION SALUD Y ATENCION DE MENORES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4868,12 +4856,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4883,13 +4871,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>48077.59</v>
+        <v>16455.28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1456839-3-CM26</t>
+          <t>425-974-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4899,27 +4887,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.981.420-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS COPIHUES</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4929,12 +4917,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4944,13 +4932,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>27869.69</v>
+        <v>24494.68</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3326-47-CM26</t>
+          <t>3326-606-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4960,12 +4948,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4990,28 +4978,32 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>37727.35</v>
+        <v>279903.74</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5148-19-CM26</t>
+          <t>1385462-299-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5021,12 +5013,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5036,12 +5028,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5051,12 +5043,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5066,13 +5058,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>54910.65</v>
+        <v>30524.89</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5153-262-CM26</t>
+          <t>2483-975-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5082,12 +5074,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5097,12 +5089,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5112,12 +5104,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5127,13 +5119,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>37912.84</v>
+        <v>37653.91</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2702-53-CM26</t>
+          <t>1216088-354-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5143,12 +5135,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5158,12 +5150,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>65.065.121-9</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5173,12 +5165,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5188,13 +5180,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>38491.58</v>
+        <v>32004.89</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1426037-23-CM26</t>
+          <t>48-425-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5204,12 +5196,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5219,12 +5211,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>70.941.900-5</t>
+          <t>61.812.000-7</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5234,12 +5226,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5249,13 +5241,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>11454.55</v>
+        <v>26749.82</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1456837-6-CM26</t>
+          <t>2455-213-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5265,12 +5257,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5280,12 +5272,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.981.450-9</t>
+          <t>69.071.000-5</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LA QUEBRADA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5295,12 +5287,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5310,13 +5302,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>26045.77</v>
+        <v>10616.58</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1107276-37-CM26</t>
+          <t>2560-127-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5326,27 +5318,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5356,28 +5348,32 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>26204.45</v>
+        <v>95375.27</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3658-84-CM26</t>
+          <t>1404452-2-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5387,12 +5383,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5402,12 +5398,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.072.800-1</t>
+          <t>65.060.484-9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALERA DE TANGO</t>
+          <t>ASOCIACION DE MUNICIPALIDADES PARQUE CORDILLERA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5417,12 +5413,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5432,13 +5428,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>22859.85</v>
+        <v>28936.25</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>29-1421-CM26</t>
+          <t>2560-141-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5448,27 +5444,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5478,28 +5474,32 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>50773.11</v>
+        <v>124455.56</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>606-100-CM26</t>
+          <t>3326-39-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5509,27 +5509,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5554,13 +5554,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>43340.19</v>
+        <v>48077.59</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>732-120-CM26</t>
+          <t>1350104-5-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5570,27 +5570,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.701.000-3</t>
+          <t>65.084.447-5</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+          <t>ASOCIACIÓN DE MUNICIPALIDADES DE LA PROVINCIA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5600,12 +5600,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5615,13 +5615,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>36148.24</v>
+        <v>21954.15</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1456841-13-CM26</t>
+          <t>1456839-3-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.981.470-3</t>
+          <t>61.981.420-7</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TALAGANTE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS COPIHUES</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5676,13 +5676,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>25376.45</v>
+        <v>27869.69</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>732-118-CM26</t>
+          <t>3326-47-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.701.000-3</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5737,13 +5737,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>36148.24</v>
+        <v>37727.35</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3577-31-CM26</t>
+          <t>5148-19-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5753,27 +5753,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.929.100-K</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Direccion Admin. Salud Municipal Florida</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5798,13 +5798,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>18749.18</v>
+        <v>54910.65</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5153-446-CM26</t>
+          <t>5153-262-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5844,12 +5844,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5859,13 +5859,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>13748.51</v>
+        <v>37912.84</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2702-93-CM26</t>
+          <t>2702-53-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5920,13 +5920,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>12965.98</v>
+        <v>38491.58</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3827-184-CM26</t>
+          <t>1426037-23-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.261.400-3</t>
+          <t>70.941.900-5</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5981,13 +5981,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>27790.1</v>
+        <v>11454.55</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>528208-29-CM26</t>
+          <t>1456837-6-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>61.981.450-9</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LA QUEBRADA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6042,13 +6042,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>26503.91</v>
+        <v>26045.77</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>48-48-CM26</t>
+          <t>1107276-37-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.812.000-7</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
+          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6103,13 +6103,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>26390.2</v>
+        <v>26204.45</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3827-193-CM26</t>
+          <t>3658-84-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.261.400-3</t>
+          <t>69.072.800-1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
+          <t>I MUNICIPALIDAD DE CALERA DE TANGO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6164,13 +6164,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>52618.21</v>
+        <v>22859.85</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2731-223-CM26</t>
+          <t>29-1421-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6180,27 +6180,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6225,13 +6225,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>17568.13</v>
+        <v>50773.11</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5190-115-CM26</t>
+          <t>732-120-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>60.506.011-0</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6286,13 +6286,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>23948.71</v>
+        <v>36148.24</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1447930-82-CM26</t>
+          <t>606-100-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6307,22 +6307,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.999.390-K</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6332,12 +6332,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6347,13 +6347,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>27041.45</v>
+        <v>43340.19</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2279-93-CM26</t>
+          <t>1456841-13-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>61.981.470-3</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TALAGANTE</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6408,13 +6408,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>30905.89</v>
+        <v>25376.45</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2789-106-CM26</t>
+          <t>732-118-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.072.600-9</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAINE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6469,28 +6469,28 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>20838.73</v>
+        <v>36148.24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2731-259-CM26</t>
+          <t>3577-31-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6500,12 +6500,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>61.929.100-K</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>Direccion Admin. Salud Municipal Florida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6515,12 +6515,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6530,33 +6530,33 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>29736.01</v>
+        <v>18749.18</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5441-171-CM26</t>
+          <t>5153-446-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6591,43 +6591,43 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>13436.1</v>
+        <v>13748.51</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>539119-1130-CM26</t>
+          <t>2702-93-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6652,43 +6652,43 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>42400.66</v>
+        <v>12965.98</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>564953-347-CM26</t>
+          <t>3827-184-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>70.902.000-5</t>
+          <t>69.261.400-3</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6713,28 +6713,28 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>42297.47</v>
+        <v>27790.1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1224957-263-CM26</t>
+          <t>528208-29-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6744,12 +6744,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>70.932.800-K</t>
+          <t>69.254.200-2</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6774,43 +6774,43 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>13959.27</v>
+        <v>26503.91</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>584264-78-CM26</t>
+          <t>3827-193-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.255.500-7</t>
+          <t>69.261.400-3</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6835,28 +6835,28 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>13428.66</v>
+        <v>52618.21</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2455-74-CM26</t>
+          <t>48-48-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.071.000-5</t>
+          <t>61.812.000-7</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6881,12 +6881,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6896,28 +6896,28 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>17357.71</v>
+        <v>26390.2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1216088-110-CM26</t>
+          <t>2731-223-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>65.065.121-9</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
+          <t>I MUNICIPALIDAD DE PENAFLOR</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6957,28 +6957,28 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>35415.26</v>
+        <v>17568.13</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1377068-70-CM26</t>
+          <t>5190-115-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6988,12 +6988,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>65.109.088-1</t>
+          <t>60.506.011-0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>LO BARNECHEA SERVICIOS</t>
+          <t>JEFATURA DE BIENESTAR (I.P)</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -7018,28 +7018,28 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>40333.05</v>
+        <v>23948.71</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2674-432-CM26</t>
+          <t>2279-93-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7064,12 +7064,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7079,28 +7079,28 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>29906.26</v>
+        <v>30905.89</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1080936-82-CM26</t>
+          <t>1447930-82-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>60.506.012-9</t>
+          <t>61.999.390-K</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondos Extrapresupuestarios Escipol </t>
+          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7140,28 +7140,28 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>74050.67999999999</v>
+        <v>27041.45</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5155-106-CM26</t>
+          <t>2789-106-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>60.504.000-4</t>
+          <t>69.072.600-9</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>I MUNICIPALIDAD DE PAINE</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7201,13 +7201,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>25361.47</v>
+        <v>20838.73</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3824-64-CM26</t>
+          <t>2731-259-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7217,27 +7217,27 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.261.400-3</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
+          <t>I MUNICIPALIDAD DE PENAFLOR</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7262,13 +7262,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>41281.73</v>
+        <v>29736.01</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>29-1644-CM26</t>
+          <t>5441-171-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7278,12 +7278,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>57146.37</v>
+        <v>13436.1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3567-278-CM26</t>
+          <t>539119-1130-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7339,27 +7339,27 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.150.700-9</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FLORIDA</t>
+          <t>Carabineros de Chile - Dirección de Bienestar</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7384,13 +7384,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>39491.98</v>
+        <v>42400.66</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>324-281-CM26</t>
+          <t>564953-347-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.255.000-5</t>
+          <t>70.902.000-5</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CERRILLOS</t>
+          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7430,12 +7430,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7445,13 +7445,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>51364.08</v>
+        <v>42297.47</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>324-289-CM26</t>
+          <t>1224957-263-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7461,27 +7461,27 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.255.000-5</t>
+          <t>70.932.800-K</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CERRILLOS</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>25089.9</v>
+        <v>13959.27</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3567-317-CM26</t>
+          <t>584264-78-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.150.700-9</t>
+          <t>69.255.500-7</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FLORIDA</t>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7567,13 +7567,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>77801.52</v>
+        <v>13428.66</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2674-509-CM26</t>
+          <t>2455-74-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7583,12 +7583,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7598,12 +7598,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>69.071.000-5</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7628,13 +7628,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>37465.27</v>
+        <v>17357.71</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3416-328-CM26</t>
+          <t>1216088-110-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7644,27 +7644,27 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.101.017-6</t>
+          <t>65.065.121-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>Callegari Ltda.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>84.916.800-2</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7689,13 +7689,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>73521.55</v>
+        <v>35415.26</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2345-260-CM26</t>
+          <t>1377068-70-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7705,27 +7705,27 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>65.109.088-1</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>LO BARNECHEA SERVICIOS</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7750,13 +7750,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>27811.39</v>
+        <v>40333.05</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2345-261-CM26</t>
+          <t>2674-432-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7766,27 +7766,27 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7811,13 +7811,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>601.49</v>
+        <v>29906.26</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>642028-37-CM26</t>
+          <t>1080936-82-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>60.506.012-9</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+          <t xml:space="preserve">Fondos Extrapresupuestarios Escipol </t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7872,13 +7872,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>30155.34</v>
+        <v>74050.67999999999</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2963-69-CM26</t>
+          <t>5155-106-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7888,27 +7888,27 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.072.400-6</t>
+          <t>60.504.000-4</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA GRANJA</t>
+          <t>Servicio Electoral</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7933,13 +7933,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>40031.46</v>
+        <v>25361.47</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5240-180-SE26</t>
+          <t>3824-64-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.261.400-3</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7979,32 +7979,28 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>81.318.700-0</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>121520.79</v>
+        <v>41281.73</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2483-461-CM26</t>
+          <t>29-1644-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8014,27 +8010,27 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8044,12 +8040,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8059,13 +8055,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>15908.52</v>
+        <v>57146.37</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>564953-704-CM26</t>
+          <t>3567-278-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8075,12 +8071,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8090,12 +8086,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>70.902.000-5</t>
+          <t>69.150.700-9</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8105,12 +8101,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8120,13 +8116,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>75440.33</v>
+        <v>39491.98</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5240-169-CM26</t>
+          <t>324-281-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8136,12 +8132,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8151,12 +8147,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.255.000-5</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE CERRILLOS</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8181,13 +8177,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>166290.37</v>
+        <v>51364.08</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1077195-69-CM26</t>
+          <t>324-289-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8197,12 +8193,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8212,12 +8208,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>69.255.000-5</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Administración de Fondos de Terceros</t>
+          <t>I MUNICIPALIDAD DE CERRILLOS</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8227,12 +8223,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8242,13 +8238,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>32391.89</v>
+        <v>25089.9</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1077195-70-CM26</t>
+          <t>3567-317-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8258,12 +8254,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8273,12 +8269,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>69.150.700-9</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Administración de Fondos de Terceros</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8288,12 +8284,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8303,13 +8299,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>682.79</v>
+        <v>77801.52</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1590-206-CM26</t>
+          <t>2674-509-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8319,27 +8315,27 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.301.000-9</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8349,12 +8345,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8364,13 +8360,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>22354.83</v>
+        <v>37465.27</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1422035-16-CM26</t>
+          <t>3416-328-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8380,27 +8376,27 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>65.034.681-5</t>
+          <t>61.101.017-6</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DEL MAULE</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8410,12 +8406,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8425,13 +8421,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>31707.78</v>
+        <v>73521.55</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1216088-218-CM26</t>
+          <t>2345-260-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8441,12 +8437,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8456,12 +8452,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>65.065.121-9</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8471,12 +8467,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8486,13 +8482,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>47211.13</v>
+        <v>27811.39</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2963-81-CM26</t>
+          <t>2345-261-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8502,12 +8498,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8517,12 +8513,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.072.400-6</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA GRANJA</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8532,12 +8528,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8547,6 +8543,742 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
+        <v>601.49</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>642028-37-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>71.293.900-1</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>30155.34</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2963-69-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>69.072.400-6</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA GRANJA</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>77.461.290-4</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>40031.46</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>5240-180-SE26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>61.938.500-4</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>121520.79</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2483-461-CM26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>69.071.300-4</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>15908.52</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>564953-704-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>70.902.000-5</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>75440.33</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>5240-169-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>61.938.500-4</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>166290.37</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1077195-69-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>82.983.100-7</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Administración de Fondos de Terceros</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>32391.89</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1077195-70-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>82.983.100-7</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Administración de Fondos de Terceros</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>682.79</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1590-206-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>61.301.000-9</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>22354.83</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1422035-16-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>65.034.681-5</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DEL MAULE</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>31707.78</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1216088-218-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>65.065.121-9</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>47211.13</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2963-81-CM26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>69.072.400-6</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA GRANJA</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
         <v>17301.41</v>
       </c>
     </row>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/metropolitana.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/metropolitana.xlsx
@@ -562,7 +562,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1533,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1598,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1724,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1789,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1854,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1919,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2045,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2110,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2175,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2240,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2305,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2431,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2496,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2561,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2626,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2691,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2817,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2882,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2947,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3012,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3077,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3142,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3207,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3333,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3398,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3463,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3528,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3593,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3719,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3784,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3849,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3914,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +3979,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4044,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4170,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4235,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4300,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4426,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4552,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4617,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4470,7 +4682,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4808,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4653,7 +4873,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4714,7 +4938,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4775,7 +5003,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +5068,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4958,7 +5194,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5259,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5324,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5450,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5263,7 +5515,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5324,7 +5580,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5645,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5710,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5775,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5568,7 +5840,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5694,7 +5970,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5820,7 +6100,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5881,7 +6165,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6072,7 +6360,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6133,7 +6425,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6194,7 +6490,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6255,7 +6555,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6316,7 +6620,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6377,7 +6685,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6438,7 +6750,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6499,7 +6815,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6560,7 +6880,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6621,7 +6945,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6682,7 +7010,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6743,7 +7075,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6869,7 +7205,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6930,7 +7270,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6991,7 +7335,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7052,7 +7400,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7113,7 +7465,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7174,7 +7530,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7235,7 +7595,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7361,7 +7725,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7422,7 +7790,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7483,7 +7855,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7544,7 +7920,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7605,7 +7985,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7918,7 +8302,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8040,7 +8428,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8101,7 +8493,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8162,7 +8558,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8223,7 +8623,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8284,7 +8688,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8345,7 +8753,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8406,7 +8818,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8467,7 +8883,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8528,7 +8948,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8650,7 +9074,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8711,7 +9139,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8772,7 +9204,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8833,7 +9269,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8894,7 +9334,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8955,7 +9399,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9081,7 +9529,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9142,7 +9594,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9203,7 +9659,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9264,7 +9724,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9325,7 +9789,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9386,7 +9854,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9447,7 +9919,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9508,7 +9984,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9569,7 +10049,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9630,7 +10114,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9691,7 +10179,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9752,7 +10244,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9813,7 +10309,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9939,7 +10439,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10000,7 +10504,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10061,7 +10569,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10122,7 +10634,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10183,7 +10699,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10244,7 +10764,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10500,7 +11024,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10561,7 +11089,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10622,7 +11154,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10683,7 +11219,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10805,7 +11345,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10866,7 +11410,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10988,7 +11536,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11049,7 +11601,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11110,7 +11666,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11171,7 +11731,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11232,7 +11796,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11293,7 +11861,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11354,7 +11926,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11415,7 +11991,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11476,7 +12056,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11537,7 +12121,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11598,7 +12186,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11659,7 +12251,11 @@
           <t>96.564.810-0</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11720,7 +12316,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11781,7 +12381,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11968,7 +12572,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12029,7 +12637,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12090,7 +12702,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12151,7 +12767,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12212,7 +12832,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12334,7 +12958,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12395,7 +13023,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12647,7 +13279,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12834,7 +13470,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12895,7 +13535,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12956,7 +13600,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13017,7 +13665,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13139,7 +13791,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13200,7 +13856,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13383,7 +14043,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13444,7 +14108,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13505,7 +14173,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13566,7 +14238,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13627,7 +14303,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13688,7 +14368,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13749,7 +14433,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13810,7 +14498,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13871,7 +14563,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13932,7 +14628,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14054,7 +14754,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14115,7 +14819,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14176,7 +14884,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14237,7 +14949,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14359,7 +15075,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14420,7 +15140,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14546,7 +15270,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14607,7 +15335,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14668,7 +15400,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14729,7 +15465,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14851,7 +15591,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14912,7 +15656,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15103,7 +15851,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15164,7 +15916,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15225,7 +15981,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15347,7 +16107,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15408,7 +16172,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15469,7 +16237,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15530,7 +16302,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15591,7 +16367,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15717,7 +16497,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15778,7 +16562,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15839,7 +16627,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15900,7 +16692,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15961,7 +16757,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16022,7 +16822,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16083,7 +16887,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16144,7 +16952,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16205,7 +17017,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16266,7 +17082,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16327,7 +17147,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16388,7 +17212,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16510,7 +17338,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16571,7 +17403,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16697,7 +17533,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16758,7 +17598,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16941,7 +17785,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17002,7 +17850,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17063,7 +17915,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17124,7 +17980,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17185,7 +18045,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17376,7 +18240,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17502,7 +18370,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17628,7 +18500,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17689,7 +18565,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17811,7 +18691,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17872,7 +18756,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18059,7 +18947,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18185,7 +19077,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18246,7 +19142,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18307,7 +19207,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18368,7 +19272,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18429,7 +19337,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18490,7 +19402,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18551,7 +19467,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18612,7 +19532,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18673,7 +19597,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18734,7 +19662,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18795,7 +19727,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18856,7 +19792,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18917,7 +19857,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19100,7 +20044,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19161,7 +20109,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19222,7 +20174,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19405,7 +20361,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19466,7 +20426,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19527,7 +20491,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19588,7 +20556,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19649,7 +20621,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19771,7 +20747,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19832,7 +20812,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19893,7 +20877,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19954,7 +20942,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20076,7 +21068,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20137,7 +21133,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20259,7 +21259,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20320,7 +21324,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20381,7 +21389,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20442,7 +21454,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20503,7 +21519,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20686,7 +21706,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20869,7 +21893,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20930,7 +21958,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20991,7 +22023,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21113,7 +22149,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21174,7 +22214,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21300,7 +22344,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21361,7 +22409,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21605,7 +22657,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21666,7 +22722,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21727,7 +22787,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21788,7 +22852,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21849,7 +22917,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21910,7 +22982,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21971,7 +23047,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22032,7 +23112,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22093,7 +23177,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22154,7 +23242,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22215,7 +23307,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22276,7 +23372,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22337,7 +23437,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22398,7 +23502,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22459,7 +23567,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22520,7 +23632,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22581,7 +23697,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22642,7 +23762,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22764,7 +23888,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22825,7 +23953,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22886,7 +24018,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22947,7 +24083,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23008,7 +24148,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23069,7 +24213,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23191,7 +24339,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23252,7 +24404,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23313,7 +24469,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23374,7 +24534,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23435,7 +24599,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23561,7 +24729,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23622,7 +24794,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23683,7 +24859,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23744,7 +24924,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23805,7 +24989,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23866,7 +25054,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24049,7 +25241,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24110,7 +25306,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24171,7 +25371,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24232,7 +25436,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/metropolitana.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/metropolitana.xlsx
@@ -21198,7 +21198,11 @@
           <t>84.916.800-2</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/metropolitana.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M388"/>
+  <dimension ref="A1:M403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1871,7 +1871,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2732-8-CM25</t>
+          <t>5155-39-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>60.504.000-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1911,32 +1911,28 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>22379.91</v>
+        <v>47345.24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5155-39-CM25</t>
+          <t>2732-8-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1956,17 +1952,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.504.000-4</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO ELECTORAL</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1976,22 +1972,26 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>47345.24</v>
+        <v>22379.91</v>
       </c>
     </row>
     <row r="25">
@@ -2448,7 +2448,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5251-233-CM25</t>
+          <t>895072-9-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2468,17 +2468,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70.729.100-1</t>
+          <t>61.980.540-2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
+          <t>SUBSECRETARIA DE EDUCACION PARVULARIA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2488,17 +2488,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>70484.91</v>
+        <v>30687.44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>895072-9-CM25</t>
+          <t>2702-87-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2533,17 +2533,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.980.540-2</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION PARVULARIA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2553,17 +2553,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2572,13 +2572,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>30687.44</v>
+        <v>35620.65</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2702-87-CM25</t>
+          <t>5251-233-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>70.729.100-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2637,13 +2637,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>35620.65</v>
+        <v>70484.91</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>85-101-CM25</t>
+          <t>85-100-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2683,32 +2683,28 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>24532.86</v>
+        <v>49500.74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>85-100-CM25</t>
+          <t>85-101-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2748,22 +2744,26 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>49500.74</v>
+        <v>24532.86</v>
       </c>
     </row>
     <row r="37">
@@ -3671,7 +3671,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1375761-3-CM25</t>
+          <t>5520-1768-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3691,17 +3691,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3711,17 +3711,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3730,13 +3730,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>25045.24</v>
+        <v>51505.23</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1375753-10-CM25</t>
+          <t>1375761-3-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.981.290-5</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS ANDES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3795,13 +3795,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>25104.37</v>
+        <v>25045.24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5520-1768-CM25</t>
+          <t>1375753-10-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3821,17 +3821,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.290-5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS ANDES</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>51505.23</v>
+        <v>25104.37</v>
       </c>
     </row>
     <row r="54">
@@ -3931,7 +3931,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>721703-112-CM25</t>
+          <t>1389488-5-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.980.230-6</t>
+          <t>61.981.320-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>AGENCIA DE CALIDAD DE LA EDUCACION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LOS ÁLAMOS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3990,13 +3990,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>49437.8</v>
+        <v>24660.67</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1389488-5-CM25</t>
+          <t>1867-34-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4021,12 +4021,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.981.320-0</t>
+          <t>61.110.000-0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LOS ÁLAMOS</t>
+          <t>DIRECCION GENERAL DE MOVILIZACIONN NACIONAL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4036,32 +4036,28 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>24660.67</v>
+        <v>24168.72</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1867-34-CM25</t>
+          <t>721703-112-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4086,12 +4082,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.110.000-0</t>
+          <t>61.980.230-6</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE MOVILIZACIONN NACIONAL</t>
+          <t>AGENCIA DE CALIDAD DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4101,22 +4097,26 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>24168.72</v>
+        <v>49437.8</v>
       </c>
     </row>
     <row r="58">
@@ -4187,7 +4187,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4499-50-CM25</t>
+          <t>858-135-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.073.100-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4246,13 +4246,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>34092.42</v>
+        <v>64221.39</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3326-130-CM25</t>
+          <t>2483-224-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4272,17 +4272,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4292,32 +4292,28 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>40623.8</v>
+        <v>111263.11</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2483-224-CM25</t>
+          <t>4499-50-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4337,17 +4333,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>69.073.100-2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4357,28 +4353,32 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>81.318.700-0</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>111263.11</v>
+        <v>34092.42</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>858-135-CM25</t>
+          <t>3326-130-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4437,13 +4437,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>64221.39</v>
+        <v>40623.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1375758-8-CM25</t>
+          <t>1080936-81-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>60.506.012-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4483,28 +4483,32 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>22569.91</v>
+        <v>22502.88</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1080936-81-CM25</t>
+          <t>1375758-8-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4529,12 +4533,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>60.506.012-9</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4544,26 +4548,22 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>91.139.000-0</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>22502.88</v>
+        <v>22569.91</v>
       </c>
     </row>
     <row r="65">
@@ -4634,7 +4634,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1214102-704-CM25</t>
+          <t>5190-161-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4654,17 +4654,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>70.835.200-4</t>
+          <t>60.506.011-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE PUDAHUEL</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4674,17 +4674,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>10160.9</v>
+        <v>35760.18</v>
       </c>
     </row>
     <row r="67">
@@ -4760,7 +4760,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5190-161-CM25</t>
+          <t>1214102-704-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4780,17 +4780,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>60.506.011-0</t>
+          <t>70.835.200-4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4800,17 +4800,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>35760.18</v>
+        <v>10160.9</v>
       </c>
     </row>
     <row r="69">
@@ -5146,7 +5146,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1044-24-CM25</t>
+          <t>870-124-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5166,17 +5166,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5186,32 +5186,28 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>35180.58</v>
+        <v>22154.58</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5506-5-CM25</t>
+          <t>1044-24-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5231,17 +5227,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5251,17 +5247,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5270,13 +5266,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>22948.12</v>
+        <v>35180.58</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3326-158-CM25</t>
+          <t>5506-5-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5301,12 +5297,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5316,17 +5312,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5335,13 +5331,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>23626.12</v>
+        <v>22948.12</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>870-124-CM25</t>
+          <t>3326-158-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5366,12 +5362,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5381,28 +5377,32 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>22154.58</v>
+        <v>23626.12</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1375757-7-CM25</t>
+          <t>1375754-19-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>61.981.260-3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS PARQUES</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5442,17 +5442,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5461,13 +5461,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>23025.78</v>
+        <v>21902.12</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1375754-19-CM25</t>
+          <t>1375757-7-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.981.260-3</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS PARQUES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5507,17 +5507,17 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>21902.12</v>
+        <v>23025.78</v>
       </c>
     </row>
     <row r="80">
@@ -5597,7 +5597,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3326-172-CM25</t>
+          <t>3625-5-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5617,17 +5617,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.072.300-k</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE SAN JOSE DE MAIPO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5656,13 +5656,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>25298.63</v>
+        <v>24911.82</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3625-5-CM25</t>
+          <t>3326-172-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.072.300-k</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JOSE DE MAIPO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>24911.82</v>
+        <v>25298.63</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>29-146-CM25</t>
+          <t>2702-189-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5747,17 +5747,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5767,17 +5767,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>49898.67</v>
+        <v>160809.31</v>
       </c>
     </row>
     <row r="84">
@@ -5857,7 +5857,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2702-189-CM25</t>
+          <t>29-146-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5877,17 +5877,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5897,17 +5897,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5916,13 +5916,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>160809.31</v>
+        <v>49898.67</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3326-179-CM25</t>
+          <t>1018-80-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5942,17 +5942,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5962,17 +5962,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5981,13 +5981,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>20551.71</v>
+        <v>113226.34</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1018-80-CM25</t>
+          <t>3326-179-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6007,17 +6007,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6027,17 +6027,17 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6046,7 +6046,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>113226.34</v>
+        <v>20551.71</v>
       </c>
     </row>
     <row r="88">
@@ -7807,7 +7807,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4099-316-CM25</t>
+          <t>1211839-7256-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7827,17 +7827,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.073.300-5</t>
+          <t>70.856.400-1</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA PINTO</t>
+          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7866,13 +7866,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>12293.35</v>
+        <v>27864.28</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1211839-7256-CM25</t>
+          <t>976-171-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7897,12 +7897,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>70.856.400-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>27864.28</v>
+        <v>27383.7</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>976-171-CM25</t>
+          <t>4099-316-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7957,17 +7957,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.073.300-5</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE MARIA PINTO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7996,7 +7996,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>27383.7</v>
+        <v>12293.35</v>
       </c>
     </row>
     <row r="118">
@@ -8254,7 +8254,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3326-259-CM25</t>
+          <t>528208-122-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.254.200-2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8294,32 +8294,28 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>19259.23</v>
+        <v>18742.22</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>528208-122-CM25</t>
+          <t>2702-263-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8339,17 +8335,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8359,28 +8355,32 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>18742.22</v>
+        <v>36475.73</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2702-263-CM25</t>
+          <t>3326-259-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8400,17 +8400,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8420,17 +8420,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8439,7 +8439,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>36475.73</v>
+        <v>19259.23</v>
       </c>
     </row>
     <row r="125">
@@ -8705,7 +8705,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>587-416-CM25</t>
+          <t>587-419-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8764,13 +8764,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>29131.04</v>
+        <v>27754.17</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>587-419-CM25</t>
+          <t>587-416-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>27754.17</v>
+        <v>29131.04</v>
       </c>
     </row>
     <row r="131">
@@ -9156,7 +9156,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5613-210-CM25</t>
+          <t>1044-49-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>DERCOMAQ SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>96.545.450-0</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -9215,13 +9215,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>38050.25</v>
+        <v>66160.02</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3326-298-CM25</t>
+          <t>5613-210-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9241,17 +9241,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9261,17 +9261,17 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9280,13 +9280,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>27750.29</v>
+        <v>38050.25</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1044-49-CM25</t>
+          <t>3326-298-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9306,17 +9306,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9326,17 +9326,17 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>DERCOMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>96.545.450-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>66160.02</v>
+        <v>27750.29</v>
       </c>
     </row>
     <row r="139">
@@ -9416,7 +9416,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2392-4410-CM25</t>
+          <t>3326-318-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9436,17 +9436,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.254.900-7</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PEDRO AGUIRRE CERDA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>80910.36</v>
+        <v>20521.92</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3326-318-CM25</t>
+          <t>2392-4410-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9501,17 +9501,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.254.900-7</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD PEDRO AGUIRRE CERDA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9540,13 +9540,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>20521.92</v>
+        <v>80910.36</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2674-671-CM25</t>
+          <t>758004-123-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9586,17 +9586,17 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9605,13 +9605,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>32458.56</v>
+        <v>41842.64</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>758004-123-CM25</t>
+          <t>2674-671-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9636,12 +9636,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9651,17 +9651,17 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>41842.64</v>
+        <v>32458.56</v>
       </c>
     </row>
     <row r="144">
@@ -9741,7 +9741,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>618-481-CM25</t>
+          <t>618-469-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9781,17 +9781,17 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9800,13 +9800,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>28105.49</v>
+        <v>50899.84</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>618-469-CM25</t>
+          <t>618-481-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9846,17 +9846,17 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9865,13 +9865,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>50899.84</v>
+        <v>28105.49</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>654478-438-CM25</t>
+          <t>3326-340-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9896,12 +9896,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.980.140-7</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9911,17 +9911,17 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9930,13 +9930,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>25942.57</v>
+        <v>18377.44</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3326-340-CM25</t>
+          <t>654478-438-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.980.140-7</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9976,17 +9976,17 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>18377.44</v>
+        <v>25942.57</v>
       </c>
     </row>
     <row r="149">
@@ -10586,7 +10586,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1447930-118-CM25</t>
+          <t>2933-295-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10606,17 +10606,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.999.390-K</t>
+          <t>69.073.200-9</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE ALHUE</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10626,17 +10626,17 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>24757.61</v>
+        <v>19747.5</v>
       </c>
     </row>
     <row r="159">
@@ -10716,7 +10716,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2933-295-CM25</t>
+          <t>1447930-118-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10736,17 +10736,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>69.073.200-9</t>
+          <t>61.999.390-K</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALHUE</t>
+          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10756,17 +10756,17 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>19747.5</v>
+        <v>24757.61</v>
       </c>
     </row>
     <row r="161">
@@ -11171,7 +11171,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2702-393-CM25</t>
+          <t>618-405-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11196,12 +11196,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11211,32 +11211,28 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>35595.78</v>
+        <v>22261.38</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>618-405-CM25</t>
+          <t>2702-393-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11261,12 +11257,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11276,22 +11272,26 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>22261.38</v>
+        <v>35595.78</v>
       </c>
     </row>
     <row r="169">
@@ -11553,7 +11553,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1271356-151-CM25</t>
+          <t>1375760-18-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>70.954.200-1</t>
+          <t>61.981.310-3</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11593,17 +11593,17 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -11612,13 +11612,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>27998.49</v>
+        <v>23039.99</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1375760-18-CM25</t>
+          <t>1271356-151-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11643,12 +11643,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.981.310-3</t>
+          <t>70.954.200-1</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11658,17 +11658,17 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -11677,13 +11677,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>23039.99</v>
+        <v>27998.49</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5542-100-CM25</t>
+          <t>5613-280-CM25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11723,17 +11723,17 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -11742,13 +11742,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>37803.07</v>
+        <v>34714.23</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>5613-280-CM25</t>
+          <t>5542-100-CM25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11788,17 +11788,17 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11807,7 +11807,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>34714.23</v>
+        <v>37803.07</v>
       </c>
     </row>
     <row r="177">
@@ -12138,7 +12138,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1098710-375-CM25</t>
+          <t>1447930-203-CM25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12158,17 +12158,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>62.000.740-4</t>
+          <t>61.999.390-K</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
+          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12178,17 +12178,17 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -12197,13 +12197,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>53818.46</v>
+        <v>20219.02</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3824-154-CM25</t>
+          <t>1098710-375-CM25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12223,17 +12223,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>69.261.400-3</t>
+          <t>62.000.740-4</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
+          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12243,12 +12243,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Guillermo Morales Ltda</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>96.564.810-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -12262,13 +12262,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>32938.28</v>
+        <v>53818.46</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1447930-203-CM25</t>
+          <t>3824-154-CM25</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12293,12 +12293,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.999.390-K</t>
+          <t>69.261.400-3</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12308,17 +12308,17 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Guillermo Morales Ltda</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.564.810-0</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -12327,13 +12327,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>20219.02</v>
+        <v>32938.28</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>4949-117-CM25</t>
+          <t>1020-327-CM25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12353,17 +12353,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.101.045-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -12392,13 +12392,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>35224.37</v>
+        <v>80696.36</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1020-327-CM25</t>
+          <t>4949-117-CM25</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12418,17 +12418,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.101.045-1</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>80696.36</v>
+        <v>35224.37</v>
       </c>
     </row>
     <row r="187">
@@ -12524,7 +12524,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3416-475-CM25</t>
+          <t>979-1634-CM25</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12549,12 +12549,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.101.017-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -12583,13 +12583,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>33862.78</v>
+        <v>48009.23</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>979-1634-CM25</t>
+          <t>3416-475-CM25</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.101.017-6</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -12648,13 +12648,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>48009.23</v>
+        <v>33862.78</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5541-143-CM25</t>
+          <t>3326-450-CM25</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12674,17 +12674,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12713,13 +12713,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>16700.41</v>
+        <v>25615.13</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3326-450-CM25</t>
+          <t>5541-143-CM25</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12739,17 +12739,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>25615.13</v>
+        <v>16700.41</v>
       </c>
     </row>
     <row r="192">
@@ -13873,7 +13873,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1431841-437-CM25</t>
+          <t>978-249-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RECOLETA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13928,13 +13928,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>9349.120000000001</v>
+        <v>49396.88</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>978-249-CM25</t>
+          <t>1431841-437-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13959,12 +13959,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>49396.88</v>
+        <v>9349.120000000001</v>
       </c>
     </row>
     <row r="211">
@@ -14320,7 +14320,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>587-725-CM25</t>
+          <t>4202-35-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>69.073.900-3</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>I MUNICIPALIDAD DE CURACAVI</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14379,13 +14379,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>21135.27</v>
+        <v>29201.86</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>4202-35-CM25</t>
+          <t>587-725-CM25</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14410,12 +14410,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>69.073.900-3</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAVI</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14444,13 +14444,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>29201.86</v>
+        <v>21135.27</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3658-698-CM25</t>
+          <t>4202-38-CM25</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14475,12 +14475,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>69.072.800-1</t>
+          <t>69.073.900-3</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALERA DE TANGO</t>
+          <t>I MUNICIPALIDAD DE CURACAVI</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14490,32 +14490,28 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>29949.02</v>
+        <v>36912.16</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1062018-257-CM25</t>
+          <t>3326-526-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14535,17 +14531,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>62.000.410-3</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DEFENSORIA DE LOS DERECHOS DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14555,17 +14551,17 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -14574,13 +14570,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>21017.81</v>
+        <v>71602.11</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>3326-526-CM25</t>
+          <t>1062018-257-CM25</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14600,17 +14596,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>62.000.410-3</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DEFENSORIA DE LOS DERECHOS DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14620,17 +14616,17 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -14639,13 +14635,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>71602.11</v>
+        <v>21017.81</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>4202-38-CM25</t>
+          <t>3658-698-CM25</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14670,12 +14666,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>69.073.900-3</t>
+          <t>69.072.800-1</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAVI</t>
+          <t>I MUNICIPALIDAD DE CALERA DE TANGO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14685,22 +14681,26 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr"/>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>36912.16</v>
+        <v>29949.02</v>
       </c>
     </row>
     <row r="222">
@@ -14901,7 +14901,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1216062-1056-CM25</t>
+          <t>48-336-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14921,17 +14921,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>71.265.200-4</t>
+          <t>61.812.000-7</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Lo Prado</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14941,32 +14941,28 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>73278.81</v>
+        <v>25124.81</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>48-336-CM25</t>
+          <t>1216062-1056-CM25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14986,17 +14982,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.812.000-7</t>
+          <t>71.265.200-4</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
+          <t>Corporación Municipal de Lo Prado</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -15006,22 +15002,26 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>25124.81</v>
+        <v>73278.81</v>
       </c>
     </row>
     <row r="227">
@@ -15287,7 +15287,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>3453-590-CM25</t>
+          <t>3326-555-CM25</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -15327,17 +15327,17 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -15346,13 +15346,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>57444.75</v>
+        <v>53702.36</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>3326-555-CM25</t>
+          <t>3323-118-CM25</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -15392,17 +15392,17 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -15411,13 +15411,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>53702.36</v>
+        <v>57444.75</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>3323-118-CM25</t>
+          <t>3453-590-CM25</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15933,7 +15933,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>425-843-CM25</t>
+          <t>707428-157-CM25</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15953,17 +15953,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15973,17 +15973,17 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -15992,13 +15992,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>24064.15</v>
+        <v>33503.59</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2412-1059-CM25</t>
+          <t>425-843-CM25</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16018,17 +16018,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -16038,28 +16038,32 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr"/>
+          <t>81.318.700-0</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>10332.52</v>
+        <v>24064.15</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>707428-157-CM25</t>
+          <t>2412-1059-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16084,12 +16088,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16099,26 +16103,22 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>33503.59</v>
+        <v>10332.52</v>
       </c>
     </row>
     <row r="244">
@@ -16384,7 +16384,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>3326-545-CM25</t>
+          <t>634-1060-CM25</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16409,12 +16409,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.004.000-4</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16424,12 +16424,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -16443,7 +16443,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>77666.49000000001</v>
+        <v>35711.05</v>
       </c>
     </row>
     <row r="249">
@@ -16579,7 +16579,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>634-1060-CM25</t>
+          <t>3326-545-CM25</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16604,12 +16604,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.004.000-4</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16619,12 +16619,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -16638,13 +16638,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>35711.05</v>
+        <v>77666.49000000001</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2271-230-CM25</t>
+          <t>2767-124-CM25</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16669,12 +16669,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16703,13 +16703,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>41395.42</v>
+        <v>19547.2</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2981-1601-CM25</t>
+          <t>5890-187-CM25</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16774,7 +16774,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1447930-322-CM25</t>
+          <t>2271-230-CM25</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16794,17 +16794,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.999.390-K</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16814,17 +16814,17 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -16833,13 +16833,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>41855.37</v>
+        <v>41395.42</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2767-124-CM25</t>
+          <t>2981-1601-CM25</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16859,17 +16859,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16879,17 +16879,17 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -16898,13 +16898,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>19547.2</v>
+        <v>41933.53</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5890-187-CM25</t>
+          <t>1447930-322-CM25</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16929,12 +16929,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.999.390-K</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16944,17 +16944,17 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -16963,7 +16963,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>41933.53</v>
+        <v>41855.37</v>
       </c>
     </row>
     <row r="257">
@@ -17420,7 +17420,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1867-331-CM25</t>
+          <t>2271-234-CM25</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17440,17 +17440,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.110.000-0</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE MOVILIZACIONN NACIONAL</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -17479,13 +17479,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>167830.71</v>
+        <v>20787.03</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2271-234-CM25</t>
+          <t>1867-331-CM25</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17505,17 +17505,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.110.000-0</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>DIRECCION GENERAL DE MOVILIZACIONN NACIONAL</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17544,7 +17544,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>20787.03</v>
+        <v>167830.71</v>
       </c>
     </row>
     <row r="266">
@@ -17615,7 +17615,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>545774-87-CM25</t>
+          <t>1375760-71-CM25</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17640,12 +17640,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>69.070.800-0</t>
+          <t>61.981.310-3</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17670,13 +17670,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>20829.86</v>
+        <v>24870.24</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1375760-71-CM25</t>
+          <t>545774-87-CM25</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17701,12 +17701,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>61.981.310-3</t>
+          <t>69.070.800-0</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
+          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17731,7 +17731,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>24870.24</v>
+        <v>20829.86</v>
       </c>
     </row>
     <row r="269">
@@ -17867,7 +17867,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>3326-624-CM25</t>
+          <t>5482-152-CM25</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17887,17 +17887,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.070.500-1</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17907,17 +17907,17 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -17926,13 +17926,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>20579.89</v>
+        <v>29754.39</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>5482-152-CM25</t>
+          <t>3326-624-CM25</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17952,17 +17952,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>69.070.500-1</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUNOA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17972,17 +17972,17 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -17991,7 +17991,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>29754.39</v>
+        <v>20579.89</v>
       </c>
     </row>
     <row r="273">
@@ -18062,7 +18062,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>5240-296-CM25</t>
+          <t>979-2135-CM25</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -18082,17 +18082,17 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -18102,12 +18102,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -18121,13 +18121,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>291974.24</v>
+        <v>582696.4300000001</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>979-2135-CM25</t>
+          <t>5240-296-CM25</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18147,17 +18147,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18167,12 +18167,12 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -18186,7 +18186,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>582696.4300000001</v>
+        <v>291974.24</v>
       </c>
     </row>
     <row r="276">
@@ -18582,7 +18582,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>48-425-CM25</t>
+          <t>2483-975-CM25</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18602,17 +18602,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.812.000-7</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18622,22 +18622,26 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr"/>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>26749.82</v>
+        <v>37653.91</v>
       </c>
     </row>
     <row r="283">
@@ -18708,7 +18712,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2483-975-CM25</t>
+          <t>48-425-CM25</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18728,17 +18732,17 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>61.812.000-7</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18748,26 +18752,22 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>37653.91</v>
+        <v>26749.82</v>
       </c>
     </row>
     <row r="285">
@@ -19614,7 +19614,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1456841-13-CM26</t>
+          <t>732-120-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19639,12 +19639,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.981.470-3</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TALAGANTE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19654,12 +19654,12 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -19673,13 +19673,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>25376.45</v>
+        <v>36148.24</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>732-118-CM26</t>
+          <t>606-100-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19699,17 +19699,17 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>61.701.000-3</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19719,17 +19719,17 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -19738,13 +19738,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>36148.24</v>
+        <v>43340.19</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>732-120-CM26</t>
+          <t>732-118-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19809,7 +19809,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>606-100-CM26</t>
+          <t>1456841-13-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19829,17 +19829,17 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>61.981.470-3</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TALAGANTE</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -19849,17 +19849,17 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -19868,7 +19868,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>43340.19</v>
+        <v>25376.45</v>
       </c>
     </row>
     <row r="302">
@@ -20191,7 +20191,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>3827-193-CM26</t>
+          <t>48-48-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -20216,12 +20216,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>69.261.400-3</t>
+          <t>61.812.000-7</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -20231,12 +20231,12 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K307" t="inlineStr"/>
@@ -20246,13 +20246,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>52618.21</v>
+        <v>26390.2</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>48-48-CM26</t>
+          <t>3827-193-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20277,12 +20277,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>61.812.000-7</t>
+          <t>69.261.400-3</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -20292,12 +20292,12 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -20307,7 +20307,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>26390.2</v>
+        <v>52618.21</v>
       </c>
     </row>
     <row r="309">
@@ -20638,7 +20638,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>5441-171-CM26</t>
+          <t>2731-259-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20658,17 +20658,17 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -20678,28 +20678,32 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
-        </is>
-      </c>
-      <c r="K314" t="inlineStr"/>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>13436.1</v>
+        <v>29736.01</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2731-259-CM26</t>
+          <t>5441-171-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20719,17 +20723,17 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20739,26 +20743,22 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K315" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>91.139.000-0</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>29736.01</v>
+        <v>13436.1</v>
       </c>
     </row>
     <row r="316">
@@ -21849,7 +21849,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2345-261-CM26</t>
+          <t>642028-37-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21869,17 +21869,17 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>71.293.900-1</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -21889,17 +21889,17 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -21908,13 +21908,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>601.49</v>
+        <v>30155.34</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>642028-37-CM26</t>
+          <t>2345-261-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21934,17 +21934,17 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21954,17 +21954,17 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -21973,7 +21973,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>30155.34</v>
+        <v>601.49</v>
       </c>
     </row>
     <row r="335">
@@ -22300,7 +22300,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2483-461-CM26</t>
+          <t>564953-704-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -22325,12 +22325,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>70.902.000-5</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -22359,13 +22359,13 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>15908.52</v>
+        <v>75440.33</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>564953-704-CM26</t>
+          <t>2483-461-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22390,12 +22390,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>70.902.000-5</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Corporación de Educación y Salud de Las Condes</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22424,13 +22424,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>75440.33</v>
+        <v>15908.52</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>5240-169-CM26</t>
+          <t>1077195-70-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22450,17 +22450,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22470,12 +22470,12 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K342" t="inlineStr"/>
@@ -22485,7 +22485,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>166290.37</v>
+        <v>682.79</v>
       </c>
     </row>
     <row r="343">
@@ -22552,7 +22552,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1077195-70-CM26</t>
+          <t>5240-169-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22572,17 +22572,17 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Comisión Chilena de Energía Nuclear</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -22592,12 +22592,12 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K344" t="inlineStr"/>
@@ -22607,7 +22607,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>682.79</v>
+        <v>166290.37</v>
       </c>
     </row>
     <row r="345">
@@ -22938,7 +22938,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1224957-567-CM26</t>
+          <t>1224957-568-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -22997,13 +22997,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>17358.05</v>
+        <v>757.65</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1224957-568-CM26</t>
+          <t>1224957-567-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>757.65</v>
+        <v>17358.05</v>
       </c>
     </row>
     <row r="352">
@@ -23133,7 +23133,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1483330-6-CM26</t>
+          <t>1483330-7-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23192,13 +23192,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>26647.14</v>
+        <v>1073.16</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1483330-7-CM26</t>
+          <t>1483330-6-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -23257,7 +23257,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1073.16</v>
+        <v>26647.14</v>
       </c>
     </row>
     <row r="355">
@@ -23523,7 +23523,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>3666-34-CM26</t>
+          <t>3666-32-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23563,12 +23563,12 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
@@ -23582,13 +23582,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>360.76</v>
+        <v>736.76</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>3666-33-CM26</t>
+          <t>3666-34-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23647,13 +23647,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>19962.46</v>
+        <v>360.76</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>3666-32-CM26</t>
+          <t>3666-33-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23693,12 +23693,12 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>736.76</v>
+        <v>19962.46</v>
       </c>
     </row>
     <row r="362">
@@ -23909,7 +23909,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>759-298-CM26</t>
+          <t>759-299-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -23929,7 +23929,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -23968,13 +23968,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>25475.68</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>759-299-CM26</t>
+          <t>759-298-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -23994,7 +23994,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -24033,13 +24033,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>33.7</v>
+        <v>25475.68</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>3326-455-CM26</t>
+          <t>3326-457-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24079,12 +24079,12 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
@@ -24098,13 +24098,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>29282.78</v>
+        <v>43132.89</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>3326-457-CM26</t>
+          <t>3326-455-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24144,12 +24144,12 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
@@ -24163,7 +24163,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>43132.89</v>
+        <v>29282.78</v>
       </c>
     </row>
     <row r="369">
@@ -24640,7 +24640,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -24835,7 +24835,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -24945,7 +24945,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1483311-6-CM26</t>
+          <t>756-290-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -24970,12 +24970,12 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>61.981.480-0</t>
+          <t>60.701.000-5</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -24985,32 +24985,28 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>DERCO S.P.A</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K381" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>94.141.000-6</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr"/>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>24520.12</v>
+        <v>1235.95</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1483311-7-CM26</t>
+          <t>756-289-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -25035,12 +25031,12 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>61.981.480-0</t>
+          <t>60.701.000-5</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -25050,32 +25046,28 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>DERCO S.P.A</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K382" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>94.141.000-6</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr"/>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>1032.44</v>
+        <v>38751.05</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>756-289-CM26</t>
+          <t>1483311-7-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -25100,12 +25092,12 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>61.981.480-0</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -25115,28 +25107,32 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>DERCO S.P.A</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>94.141.000-6</t>
-        </is>
-      </c>
-      <c r="K383" t="inlineStr"/>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>38751.05</v>
+        <v>1032.44</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>756-290-CM26</t>
+          <t>1483311-6-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25161,12 +25157,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>61.981.480-0</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS VIÑEDOS</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -25176,28 +25172,32 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>DERCO S.P.A</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>94.141.000-6</t>
-        </is>
-      </c>
-      <c r="K384" t="inlineStr"/>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>1235.95</v>
+        <v>24520.12</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>29-1925-CM26</t>
+          <t>625-339-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -25212,7 +25212,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -25256,13 +25256,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>74255.63</v>
+        <v>37372.39</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>528208-102-CM26</t>
+          <t>29-1925-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -25277,22 +25277,22 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -25321,7 +25321,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>26530.31</v>
+        <v>74255.63</v>
       </c>
     </row>
     <row r="387">
@@ -25392,66 +25392,1033 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
+          <t>528208-102-CM26</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>69.254.200-2</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M388" s="2" t="n">
+        <v>26530.31</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
           <t>528208-103-CM26</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr">
+      <c r="B389" t="inlineStr">
         <is>
           <t>2239-6-LR25</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr">
+      <c r="C389" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr">
+      <c r="D389" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr">
+      <c r="E389" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr">
+      <c r="F389" t="inlineStr">
         <is>
           <t>69.254.200-2</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr">
+      <c r="G389" t="inlineStr">
         <is>
           <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
-      <c r="H388" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I388" t="inlineStr">
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
         <is>
           <t>KOVACS SPA</t>
         </is>
       </c>
-      <c r="J388" t="inlineStr">
+      <c r="J389" t="inlineStr">
         <is>
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L388" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M388" s="2" t="n">
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M389" s="2" t="n">
         <v>639.99</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>564953-1019-CM26</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>70.902.000-5</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Corporación de Educación y Salud de Las Condes</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M390" s="2" t="n">
+        <v>34035.53</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>218-487-CM26</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>69.254.600-8</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD SAN JOAQUIN</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>FK SPA</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>77.050.575-5</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M391" s="2" t="n">
+        <v>11532.97</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>1425525-32-CM26</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>62.000.560-6</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>AGENCIA NACIONAL DE CIBERSEGURIDAD</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M392" s="2" t="n">
+        <v>24839.09</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2702-474-CM26</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>69.071.800-6</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M393" s="2" t="n">
+        <v>34908.5</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>3894-87-CM26</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>69.071.400-0</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M394" s="2" t="n">
+        <v>9210.549999999999</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>584264-191-CM26</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>69.255.500-7</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M395" s="2" t="n">
+        <v>1515.35</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>584264-190-CM26</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>69.255.500-7</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M396" s="2" t="n">
+        <v>35035.02</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2345-544-CM26</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>69.070.400-5</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M397" s="2" t="n">
+        <v>87954.36</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2345-541-CM26</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>69.070.400-5</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>FINNING CHILE S A</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>91.489.000-4</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr"/>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M398" s="2" t="n">
+        <v>313878.96</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>634-714-CM26</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>61.004.000-4</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M399" s="2" t="n">
+        <v>35484.34</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>757-680-CM26</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>61.601.000-k</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M400" s="2" t="n">
+        <v>47791.65</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>3453-497-CM26</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>61.979.960-7</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M401" s="2" t="n">
+        <v>2969.49</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>3453-496-CM26</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>61.979.960-7</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M402" s="2" t="n">
+        <v>70518</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>564162-1094-CM26</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>60.911.000-7</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>TATTERSALL AUTOMOTRIZ S.A.</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>83.019.900-4</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M403" s="2" t="n">
+        <v>46725.3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/metropolitana.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/metropolitana.xlsx
@@ -1050,7 +1050,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -22125,7 +22125,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -22190,7 +22190,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -22633,7 +22633,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -22763,7 +22763,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -22893,7 +22893,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -23153,7 +23153,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -23218,7 +23218,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/metropolitana.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M403"/>
+  <dimension ref="A1:M405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2643,7 +2643,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>85-100-CM25</t>
+          <t>85-101-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2683,28 +2683,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>49500.74</v>
+        <v>24532.86</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>85-101-CM25</t>
+          <t>85-100-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2744,32 +2748,28 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>24532.86</v>
+        <v>49500.74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5251-237-CM25</t>
+          <t>3326-69-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>70.729.100-1</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2828,13 +2828,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>28580.2</v>
+        <v>28911.07</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3326-69-CM25</t>
+          <t>5251-237-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2854,17 +2854,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>70.729.100-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>28911.07</v>
+        <v>28580.2</v>
       </c>
     </row>
     <row r="39">
@@ -3671,7 +3671,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5520-1768-CM25</t>
+          <t>1375761-3-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3691,17 +3691,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3711,17 +3711,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3730,13 +3730,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>51505.23</v>
+        <v>25045.24</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1375761-3-CM25</t>
+          <t>1375753-10-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>61.981.290-5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS ANDES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3795,13 +3795,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>25045.24</v>
+        <v>25104.37</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1375753-10-CM25</t>
+          <t>5520-1768-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3821,17 +3821,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.981.290-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS ANDES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>25104.37</v>
+        <v>51505.23</v>
       </c>
     </row>
     <row r="54">
@@ -4443,7 +4443,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1080936-81-CM25</t>
+          <t>1375758-8-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>60.506.012-9</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4483,32 +4483,28 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>91.139.000-0</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>22502.88</v>
+        <v>22569.91</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1375758-8-CM25</t>
+          <t>1080936-81-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4533,12 +4529,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>60.506.012-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4548,22 +4544,26 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>22569.91</v>
+        <v>22502.88</v>
       </c>
     </row>
     <row r="65">
@@ -5146,7 +5146,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>870-124-CM25</t>
+          <t>1044-24-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5166,17 +5166,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5186,28 +5186,32 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>22154.58</v>
+        <v>35180.58</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1044-24-CM25</t>
+          <t>870-124-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5227,17 +5231,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5247,26 +5251,22 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>35180.58</v>
+        <v>22154.58</v>
       </c>
     </row>
     <row r="76">
@@ -5597,7 +5597,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3625-5-CM25</t>
+          <t>3326-172-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5617,17 +5617,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.072.300-k</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JOSE DE MAIPO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5656,13 +5656,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>24911.82</v>
+        <v>25298.63</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3326-172-CM25</t>
+          <t>3625-5-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.072.300-k</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE SAN JOSE DE MAIPO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>25298.63</v>
+        <v>24911.82</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2702-189-CM25</t>
+          <t>29-146-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5747,17 +5747,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5767,17 +5767,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>160809.31</v>
+        <v>49898.67</v>
       </c>
     </row>
     <row r="84">
@@ -5857,7 +5857,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>29-146-CM25</t>
+          <t>2702-189-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5877,17 +5877,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5897,17 +5897,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5916,13 +5916,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>49898.67</v>
+        <v>160809.31</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1018-80-CM25</t>
+          <t>5190-186-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5942,17 +5942,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.506.011-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>113226.34</v>
+        <v>27121.28</v>
       </c>
     </row>
     <row r="87">
@@ -6052,7 +6052,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5190-186-CM25</t>
+          <t>1018-80-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6072,17 +6072,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>60.506.011-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>27121.28</v>
+        <v>113226.34</v>
       </c>
     </row>
     <row r="89">
@@ -6832,7 +6832,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3474-390-CM25</t>
+          <t>3326-209-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6872,17 +6872,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6891,13 +6891,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>35603.63</v>
+        <v>22716.93</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3326-209-CM25</t>
+          <t>3474-390-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>22716.93</v>
+        <v>35603.63</v>
       </c>
     </row>
     <row r="102">
@@ -8705,7 +8705,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>587-419-CM25</t>
+          <t>587-416-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8764,13 +8764,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>27754.17</v>
+        <v>29131.04</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>587-416-CM25</t>
+          <t>587-419-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>29131.04</v>
+        <v>27754.17</v>
       </c>
     </row>
     <row r="131">
@@ -9026,7 +9026,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2702-303-CM25</t>
+          <t>3326-296-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9046,17 +9046,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -9085,13 +9085,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>27512.57</v>
+        <v>28411.88</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3326-296-CM25</t>
+          <t>2702-303-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9111,17 +9111,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9131,12 +9131,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -9150,13 +9150,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>28411.88</v>
+        <v>27512.57</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1044-49-CM25</t>
+          <t>5613-210-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>DERCOMAQ SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>96.545.450-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -9215,13 +9215,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>66160.02</v>
+        <v>38050.25</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5613-210-CM25</t>
+          <t>3326-298-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9241,17 +9241,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9261,17 +9261,17 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9280,13 +9280,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>38050.25</v>
+        <v>27750.29</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3326-298-CM25</t>
+          <t>1044-49-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9306,17 +9306,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9326,17 +9326,17 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>DERCOMAQ SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>96.545.450-0</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>27750.29</v>
+        <v>66160.02</v>
       </c>
     </row>
     <row r="139">
@@ -9871,7 +9871,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3326-340-CM25</t>
+          <t>654478-438-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9896,12 +9896,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.980.140-7</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9911,17 +9911,17 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9930,13 +9930,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>18377.44</v>
+        <v>25942.57</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>654478-438-CM25</t>
+          <t>3326-340-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.980.140-7</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9976,17 +9976,17 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>25942.57</v>
+        <v>18377.44</v>
       </c>
     </row>
     <row r="149">
@@ -10586,7 +10586,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2933-295-CM25</t>
+          <t>1447930-119-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10606,17 +10606,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.073.200-9</t>
+          <t>61.999.390-K</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALHUE</t>
+          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10626,17 +10626,17 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10645,13 +10645,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>19747.5</v>
+        <v>24219.4</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1447930-119-CM25</t>
+          <t>2933-295-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10671,17 +10671,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.999.390-K</t>
+          <t>69.073.200-9</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE ALHUE</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10691,17 +10691,17 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>24219.4</v>
+        <v>19747.5</v>
       </c>
     </row>
     <row r="160">
@@ -10781,7 +10781,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>609-329-CM25</t>
+          <t>622-417-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10806,12 +10806,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>60.805.000-0</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10821,12 +10821,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -10840,13 +10840,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>404994.09</v>
+        <v>79045.98</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>622-417-CM25</t>
+          <t>609-337-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10871,12 +10871,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>60.805.000-0</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10886,17 +10886,17 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10905,13 +10905,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>79045.98</v>
+        <v>135478.99</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>609-337-CM25</t>
+          <t>2702-392-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10931,17 +10931,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10951,17 +10951,17 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>135478.99</v>
+        <v>27035.62</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2702-392-CM25</t>
+          <t>609-329-CM25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10996,17 +10996,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -11016,17 +11016,17 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>27035.62</v>
+        <v>404994.09</v>
       </c>
     </row>
     <row r="165">
@@ -11553,7 +11553,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1375760-18-CM25</t>
+          <t>1271356-151-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.981.310-3</t>
+          <t>70.954.200-1</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11593,17 +11593,17 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -11612,13 +11612,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>23039.99</v>
+        <v>27998.49</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1271356-151-CM25</t>
+          <t>1375760-18-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11643,12 +11643,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>70.954.200-1</t>
+          <t>61.981.310-3</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11658,17 +11658,17 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -11677,13 +11677,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>27998.49</v>
+        <v>23039.99</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5613-280-CM25</t>
+          <t>584264-180-CM25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11703,17 +11703,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.255.500-7</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11723,12 +11723,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -11742,7 +11742,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>34714.23</v>
+        <v>69817.14</v>
       </c>
     </row>
     <row r="176">
@@ -11813,7 +11813,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>584264-180-CM25</t>
+          <t>5613-280-CM25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11833,17 +11833,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.255.500-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -11872,7 +11872,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>69817.14</v>
+        <v>34714.23</v>
       </c>
     </row>
     <row r="178">
@@ -13487,7 +13487,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>3326-495-CM25</t>
+          <t>3326-489-CM25</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13527,17 +13527,17 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -13546,13 +13546,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>44016.94</v>
+        <v>20419.51</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>3326-489-CM25</t>
+          <t>3326-495-CM25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13592,17 +13592,17 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -13611,13 +13611,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>20419.51</v>
+        <v>44016.94</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>707429-173-CM25</t>
+          <t>622-620-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13642,12 +13642,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.805.000-0</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13657,32 +13657,28 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>29435.93</v>
+        <v>97421.48</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>622-620-CM25</t>
+          <t>634-941-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13707,12 +13703,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>60.805.000-0</t>
+          <t>61.004.000-4</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13722,28 +13718,32 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>97421.48</v>
+        <v>30978.11</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>634-941-CM25</t>
+          <t>707429-173-CM25</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.004.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13783,17 +13783,17 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -13802,7 +13802,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>30978.11</v>
+        <v>29435.93</v>
       </c>
     </row>
     <row r="208">
@@ -13873,7 +13873,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>978-249-CM25</t>
+          <t>1431841-437-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13928,13 +13928,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>49396.88</v>
+        <v>9349.120000000001</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1431841-437-CM25</t>
+          <t>978-249-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13959,12 +13959,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RECOLETA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>9349.120000000001</v>
+        <v>49396.88</v>
       </c>
     </row>
     <row r="211">
@@ -14706,7 +14706,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>3326-535-CM25</t>
+          <t>1216062-1030-CM25</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14726,17 +14726,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>71.265.200-4</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Corporación Municipal de Lo Prado</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14746,17 +14746,17 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -14765,13 +14765,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>30610.16</v>
+        <v>43461.47</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1216062-1030-CM25</t>
+          <t>3326-535-CM25</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14791,17 +14791,17 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>71.265.200-4</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Lo Prado</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14811,17 +14811,17 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -14830,7 +14830,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>43461.47</v>
+        <v>30610.16</v>
       </c>
     </row>
     <row r="224">
@@ -14901,7 +14901,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>48-336-CM25</t>
+          <t>1216062-1056-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14921,17 +14921,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.812.000-7</t>
+          <t>71.265.200-4</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
+          <t>Corporación Municipal de Lo Prado</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14941,28 +14941,32 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>25124.81</v>
+        <v>73278.81</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1216062-1056-CM25</t>
+          <t>48-336-CM25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14982,17 +14986,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>71.265.200-4</t>
+          <t>61.812.000-7</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Lo Prado</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -15002,32 +15006,28 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>73278.81</v>
+        <v>25124.81</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>3316-318-CM25</t>
+          <t>967490-57-CM25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15052,7 +15052,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -15067,17 +15067,17 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -15086,13 +15086,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>52803.36</v>
+        <v>49325.94</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>967490-57-CM25</t>
+          <t>3316-318-CM25</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -15132,17 +15132,17 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -15151,7 +15151,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>49325.94</v>
+        <v>52803.36</v>
       </c>
     </row>
     <row r="229">
@@ -15998,7 +15998,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>425-843-CM25</t>
+          <t>2412-1059-CM25</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16018,17 +16018,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -16038,32 +16038,28 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>24064.15</v>
+        <v>10332.52</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2412-1059-CM25</t>
+          <t>425-843-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16083,17 +16079,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16103,22 +16099,26 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr"/>
+          <t>81.318.700-0</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>10332.52</v>
+        <v>24064.15</v>
       </c>
     </row>
     <row r="244">
@@ -16189,7 +16189,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>587-795-CM25</t>
+          <t>5482-144-CM25</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16209,17 +16209,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>69.070.500-1</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>25338.18</v>
+        <v>67160.3</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>5482-144-CM25</t>
+          <t>587-795-CM25</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16274,17 +16274,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>69.070.500-1</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUNOA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -16313,7 +16313,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>67160.3</v>
+        <v>25338.18</v>
       </c>
     </row>
     <row r="247">
@@ -16384,7 +16384,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>634-1060-CM25</t>
+          <t>634-1055-CM25</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16443,13 +16443,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>35711.05</v>
+        <v>71422.09</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>634-1055-CM25</t>
+          <t>1147293-331-CM25</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16469,17 +16469,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.004.000-4</t>
+          <t>70.930.000-8</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>Fundación para la Innovación Agraria</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16489,17 +16489,17 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -16508,13 +16508,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>71422.09</v>
+        <v>25237.05</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1147293-331-CM25</t>
+          <t>634-1060-CM25</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16534,17 +16534,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>70.930.000-8</t>
+          <t>61.004.000-4</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Fundación para la Innovación Agraria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16554,17 +16554,17 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -16573,7 +16573,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>25237.05</v>
+        <v>35711.05</v>
       </c>
     </row>
     <row r="251">
@@ -16969,7 +16969,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2673-227-CM25</t>
+          <t>3326-597-CM25</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16989,17 +16989,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -17009,17 +17009,17 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -17028,13 +17028,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>43996.12</v>
+        <v>50233.74</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2974-641-CM25</t>
+          <t>2673-227-CM25</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17054,17 +17054,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -17074,17 +17074,17 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -17093,13 +17093,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>46279.36</v>
+        <v>43996.12</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>29-589-CM25</t>
+          <t>2974-641-CM25</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -17139,17 +17139,17 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -17158,13 +17158,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>49083.79</v>
+        <v>46279.36</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>3326-597-CM25</t>
+          <t>29-589-CM25</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17189,12 +17189,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -17204,17 +17204,17 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -17223,7 +17223,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>50233.74</v>
+        <v>49083.79</v>
       </c>
     </row>
     <row r="261">
@@ -17615,7 +17615,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1375760-71-CM25</t>
+          <t>3326-621-CM25</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17640,12 +17640,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.981.310-3</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17655,28 +17655,32 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr"/>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>24870.24</v>
+        <v>58856.7</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>545774-87-CM25</t>
+          <t>1375760-71-CM25</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17701,12 +17705,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>69.070.800-0</t>
+          <t>61.981.310-3</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17731,13 +17735,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>20829.86</v>
+        <v>24870.24</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>545774-88-CM25</t>
+          <t>545774-87-CM25</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17757,7 +17761,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -17777,32 +17781,28 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>41931.21</v>
+        <v>20829.86</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>3326-621-CM25</t>
+          <t>545774-88-CM25</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17822,17 +17822,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.070.800-0</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17842,17 +17842,17 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -17861,7 +17861,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>58856.7</v>
+        <v>41931.21</v>
       </c>
     </row>
     <row r="271">
@@ -19614,7 +19614,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>732-120-CM26</t>
+          <t>606-100-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19634,17 +19634,17 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.701.000-3</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19654,17 +19654,17 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -19673,13 +19673,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>36148.24</v>
+        <v>43340.19</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>606-100-CM26</t>
+          <t>732-120-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19699,17 +19699,17 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>61.701.000-3</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE MINERIA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19719,17 +19719,17 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -19738,7 +19738,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>43340.19</v>
+        <v>36148.24</v>
       </c>
     </row>
     <row r="300">
@@ -20443,7 +20443,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2279-93-CM26</t>
+          <t>1447930-82-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20468,12 +20468,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>61.999.390-K</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -20483,17 +20483,17 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -20502,13 +20502,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>30905.89</v>
+        <v>27041.45</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1447930-82-CM26</t>
+          <t>2789-106-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20533,12 +20533,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>61.999.390-K</t>
+          <t>69.072.600-9</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE PAINE</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -20548,17 +20548,17 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -20567,13 +20567,13 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>27041.45</v>
+        <v>20838.73</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2789-106-CM26</t>
+          <t>2279-93-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20598,12 +20598,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>69.072.600-9</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAINE</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -20613,12 +20613,12 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -20632,13 +20632,13 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>20838.73</v>
+        <v>30905.89</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2731-259-CM26</t>
+          <t>5441-171-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20658,17 +20658,17 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -20678,32 +20678,28 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>91.139.000-0</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr"/>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>29736.01</v>
+        <v>13436.1</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>5441-171-CM26</t>
+          <t>2731-259-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20723,17 +20719,17 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20743,22 +20739,26 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
-        </is>
-      </c>
-      <c r="K315" t="inlineStr"/>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>13436.1</v>
+        <v>29736.01</v>
       </c>
     </row>
     <row r="316">
@@ -21849,7 +21849,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>642028-37-CM26</t>
+          <t>2345-261-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21869,17 +21869,17 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -21889,17 +21889,17 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -21908,13 +21908,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>30155.34</v>
+        <v>601.49</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2345-261-CM26</t>
+          <t>642028-37-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21934,17 +21934,17 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>71.293.900-1</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21954,17 +21954,17 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -21973,7 +21973,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>601.49</v>
+        <v>30155.34</v>
       </c>
     </row>
     <row r="335">
@@ -22105,7 +22105,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1456836-6-CM26</t>
+          <t>1456836-7-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22164,13 +22164,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>25099.83</v>
+        <v>1422.6</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1456836-7-CM26</t>
+          <t>1456836-6-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22229,7 +22229,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>1422.6</v>
+        <v>25099.83</v>
       </c>
     </row>
     <row r="339">
@@ -23328,7 +23328,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1274189-357-CM26</t>
+          <t>1274189-358-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23387,13 +23387,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>36455.84</v>
+        <v>511.07</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1274189-358-CM26</t>
+          <t>1274189-357-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23452,7 +23452,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>511.07</v>
+        <v>36455.84</v>
       </c>
     </row>
     <row r="358">
@@ -23523,7 +23523,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>3666-32-CM26</t>
+          <t>3666-34-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23563,12 +23563,12 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
@@ -23582,13 +23582,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>736.76</v>
+        <v>360.76</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>3666-34-CM26</t>
+          <t>3666-33-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23647,13 +23647,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>360.76</v>
+        <v>19962.46</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>3666-33-CM26</t>
+          <t>3666-32-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23693,12 +23693,12 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>19962.46</v>
+        <v>736.76</v>
       </c>
     </row>
     <row r="362">
@@ -23909,7 +23909,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>759-299-CM26</t>
+          <t>759-298-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -23929,7 +23929,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -23968,13 +23968,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>33.7</v>
+        <v>25475.68</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>759-298-CM26</t>
+          <t>759-299-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -23994,7 +23994,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -24033,7 +24033,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>25475.68</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="367">
@@ -25587,7 +25587,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>218-487-CM26</t>
+          <t>1425525-32-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25607,17 +25607,17 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>69.254.600-8</t>
+          <t>62.000.560-6</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD SAN JOAQUIN</t>
+          <t>AGENCIA NACIONAL DE CIBERSEGURIDAD</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -25627,17 +25627,17 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>FK SPA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>77.050.575-5</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -25646,13 +25646,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>11532.97</v>
+        <v>24839.09</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>1425525-32-CM26</t>
+          <t>218-487-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25672,17 +25672,17 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>62.000.560-6</t>
+          <t>69.254.600-8</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>AGENCIA NACIONAL DE CIBERSEGURIDAD</t>
+          <t>I MUNICIPALIDAD SAN JOAQUIN</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25692,17 +25692,17 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>FK SPA</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>77.050.575-5</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
@@ -25711,7 +25711,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>24839.09</v>
+        <v>11532.97</v>
       </c>
     </row>
     <row r="393">
@@ -25847,7 +25847,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>584264-191-CM26</t>
+          <t>584264-190-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -25906,13 +25906,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>1515.35</v>
+        <v>35035.02</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>584264-190-CM26</t>
+          <t>584264-191-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -25971,7 +25971,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>35035.02</v>
+        <v>1515.35</v>
       </c>
     </row>
     <row r="397">
@@ -26233,7 +26233,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>3453-497-CM26</t>
+          <t>3453-496-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -26292,13 +26292,13 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>2969.49</v>
+        <v>70518</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>3453-496-CM26</t>
+          <t>3453-497-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -26357,7 +26357,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>70518</v>
+        <v>2969.49</v>
       </c>
     </row>
     <row r="403">
@@ -26419,6 +26419,132 @@
       </c>
       <c r="M403" s="2" t="n">
         <v>46725.3</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>1191688-102-CM26</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>69.255.300-4</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M404" s="2" t="n">
+        <v>260677.52</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2345-557-CM26</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>69.070.400-5</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>HVCCSA</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>76.758.790-2</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M405" s="2" t="n">
+        <v>45461.19</v>
       </c>
     </row>
   </sheetData>
